--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555195858</v>
+        <v>46157.93112106292</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112106292</v>
+        <v>46157.93136049756</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136049756</v>
+        <v>46157.93383661212</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93383661212</v>
+        <v>46157.93695366564</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93695366564</v>
+        <v>46158.2820472418</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820472418</v>
+        <v>46158.29651937223</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651937223</v>
+        <v>46158.2980706935</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980706935</v>
+        <v>46158.33370096607</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370096607</v>
+        <v>46158.37221444161</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221444161</v>
+        <v>46158.37275342253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
